--- a/artfynd/A 45350-2024 artfynd.xlsx
+++ b/artfynd/A 45350-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120522226</v>
+        <v>120522120</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463359</v>
+        <v>463320</v>
       </c>
       <c r="R2" t="n">
-        <v>6720025</v>
+        <v>6719930</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120522134</v>
+        <v>120522233</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463314</v>
+        <v>463348</v>
       </c>
       <c r="R3" t="n">
-        <v>6719914</v>
+        <v>6720041</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120522144</v>
+        <v>120522934</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463307</v>
+        <v>463154</v>
       </c>
       <c r="R4" t="n">
-        <v>6719946</v>
+        <v>6720291</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120522167</v>
+        <v>120522954</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463358</v>
+        <v>463140</v>
       </c>
       <c r="R5" t="n">
-        <v>6719920</v>
+        <v>6720298</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120522934</v>
+        <v>120522965</v>
       </c>
       <c r="B6" t="n">
         <v>91858</v>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463154</v>
+        <v>463108</v>
       </c>
       <c r="R6" t="n">
-        <v>6720291</v>
+        <v>6720174</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120522076</v>
+        <v>120522134</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463267</v>
+        <v>463314</v>
       </c>
       <c r="R7" t="n">
-        <v>6719845</v>
+        <v>6719914</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120522954</v>
+        <v>120522144</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463140</v>
+        <v>463307</v>
       </c>
       <c r="R9" t="n">
-        <v>6720298</v>
+        <v>6719946</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1525,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120522120</v>
+        <v>120522946</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,35 +1542,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463320</v>
+        <v>463159</v>
       </c>
       <c r="R10" t="n">
-        <v>6719930</v>
+        <v>6720284</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120522946</v>
+        <v>120522226</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463159</v>
+        <v>463359</v>
       </c>
       <c r="R11" t="n">
-        <v>6720284</v>
+        <v>6720025</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120522907</v>
+        <v>120522167</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,32 +1754,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463143</v>
+        <v>463358</v>
       </c>
       <c r="R12" t="n">
-        <v>6720306</v>
+        <v>6719920</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1850,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120522965</v>
+        <v>120522907</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,26 +1864,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463108</v>
+        <v>463143</v>
       </c>
       <c r="R13" t="n">
-        <v>6720174</v>
+        <v>6720306</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120522233</v>
+        <v>120522076</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463348</v>
+        <v>463267</v>
       </c>
       <c r="R14" t="n">
-        <v>6720041</v>
+        <v>6719845</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120522254</v>
+        <v>120522299</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,32 +2074,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463446</v>
+        <v>463466</v>
       </c>
       <c r="R15" t="n">
-        <v>6720099</v>
+        <v>6720132</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2170,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120522767</v>
+        <v>120522195</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2213,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463536</v>
+        <v>463428</v>
       </c>
       <c r="R16" t="n">
-        <v>6720348</v>
+        <v>6720039</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2276,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120522185</v>
+        <v>120522599</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2288,25 +2291,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2319,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463394</v>
+        <v>463495</v>
       </c>
       <c r="R17" t="n">
-        <v>6719985</v>
+        <v>6720323</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2382,7 +2385,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120522268</v>
+        <v>120522319</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2415,24 +2418,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N kvarnsjön, Dlr</t>
+          <t>N Kvarnsjön, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463461</v>
+        <v>463493</v>
       </c>
       <c r="R18" t="n">
-        <v>6720109</v>
+        <v>6720142</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2492,10 +2491,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120522319</v>
+        <v>120522747</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,26 +2507,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2535,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463493</v>
+        <v>463506</v>
       </c>
       <c r="R19" t="n">
-        <v>6720142</v>
+        <v>6720334</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2598,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120522299</v>
+        <v>120522254</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,35 +2611,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463466</v>
+        <v>463446</v>
       </c>
       <c r="R20" t="n">
-        <v>6720132</v>
+        <v>6720099</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2709,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120522747</v>
+        <v>120522185</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,32 +2719,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2754,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463506</v>
+        <v>463394</v>
       </c>
       <c r="R21" t="n">
-        <v>6720334</v>
+        <v>6719985</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2817,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120522728</v>
+        <v>120522268</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,41 +2825,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Kvarnsjön, Dlr</t>
+          <t>N kvarnsjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463492</v>
+        <v>463461</v>
       </c>
       <c r="R22" t="n">
-        <v>6720346</v>
+        <v>6720109</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120522599</v>
+        <v>120522767</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463495</v>
+        <v>463536</v>
       </c>
       <c r="R23" t="n">
-        <v>6720323</v>
+        <v>6720348</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120522195</v>
+        <v>120522728</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463428</v>
+        <v>463492</v>
       </c>
       <c r="R24" t="n">
-        <v>6720039</v>
+        <v>6720346</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>

--- a/artfynd/A 45350-2024 artfynd.xlsx
+++ b/artfynd/A 45350-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120522120</v>
+        <v>120522233</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463320</v>
+        <v>463348</v>
       </c>
       <c r="R2" t="n">
-        <v>6719930</v>
+        <v>6720041</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -786,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120522233</v>
+        <v>120522144</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463348</v>
+        <v>463307</v>
       </c>
       <c r="R3" t="n">
-        <v>6720041</v>
+        <v>6719946</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -892,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120522934</v>
+        <v>120522134</v>
       </c>
       <c r="B4" t="n">
         <v>91858</v>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463154</v>
+        <v>463314</v>
       </c>
       <c r="R4" t="n">
-        <v>6720291</v>
+        <v>6719914</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120522954</v>
+        <v>120522934</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463140</v>
+        <v>463154</v>
       </c>
       <c r="R5" t="n">
-        <v>6720298</v>
+        <v>6720291</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120522965</v>
+        <v>120522923</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,26 +1115,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463108</v>
+        <v>463167</v>
       </c>
       <c r="R6" t="n">
-        <v>6720174</v>
+        <v>6720285</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120522134</v>
+        <v>120522946</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1219,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463314</v>
+        <v>463159</v>
       </c>
       <c r="R7" t="n">
-        <v>6719914</v>
+        <v>6720284</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1316,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120522923</v>
+        <v>120522226</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,32 +1325,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463167</v>
+        <v>463359</v>
       </c>
       <c r="R8" t="n">
-        <v>6720285</v>
+        <v>6720025</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120522144</v>
+        <v>120522965</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463307</v>
+        <v>463108</v>
       </c>
       <c r="R9" t="n">
-        <v>6719946</v>
+        <v>6720174</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1530,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120522946</v>
+        <v>120522954</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463159</v>
+        <v>463140</v>
       </c>
       <c r="R10" t="n">
-        <v>6720284</v>
+        <v>6720298</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1636,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120522226</v>
+        <v>120522167</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463359</v>
+        <v>463358</v>
       </c>
       <c r="R11" t="n">
-        <v>6720025</v>
+        <v>6719920</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1742,7 +1737,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120522167</v>
+        <v>120522076</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463358</v>
+        <v>463267</v>
       </c>
       <c r="R12" t="n">
-        <v>6719920</v>
+        <v>6719845</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1956,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120522076</v>
+        <v>120522120</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,30 +1963,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463267</v>
+        <v>463320</v>
       </c>
       <c r="R14" t="n">
-        <v>6719845</v>
+        <v>6719930</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120522299</v>
+        <v>120522728</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,35 +2074,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2110,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463466</v>
+        <v>463492</v>
       </c>
       <c r="R15" t="n">
-        <v>6720132</v>
+        <v>6720346</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2173,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120522195</v>
+        <v>120522747</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,30 +2180,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2216,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463428</v>
+        <v>463506</v>
       </c>
       <c r="R16" t="n">
-        <v>6720039</v>
+        <v>6720334</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2279,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120522599</v>
+        <v>120522767</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,25 +2288,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463495</v>
+        <v>463536</v>
       </c>
       <c r="R17" t="n">
-        <v>6720323</v>
+        <v>6720348</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2491,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120522747</v>
+        <v>120522268</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,39 +2504,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Kvarnsjön, Dlr</t>
+          <t>N kvarnsjön, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463506</v>
+        <v>463461</v>
       </c>
       <c r="R19" t="n">
-        <v>6720334</v>
+        <v>6720109</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2599,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120522254</v>
+        <v>120522599</v>
       </c>
       <c r="B20" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,28 +2614,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2644,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463446</v>
+        <v>463495</v>
       </c>
       <c r="R20" t="n">
-        <v>6720099</v>
+        <v>6720323</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2813,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120522268</v>
+        <v>120522299</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,45 +2822,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N kvarnsjön, Dlr</t>
+          <t>N Kvarnsjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463461</v>
+        <v>463466</v>
       </c>
       <c r="R22" t="n">
-        <v>6720109</v>
+        <v>6720132</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2923,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120522767</v>
+        <v>120522254</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,30 +2933,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463536</v>
+        <v>463446</v>
       </c>
       <c r="R23" t="n">
-        <v>6720348</v>
+        <v>6720099</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120522728</v>
+        <v>120522195</v>
       </c>
       <c r="B24" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463492</v>
+        <v>463428</v>
       </c>
       <c r="R24" t="n">
-        <v>6720346</v>
+        <v>6720039</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>

--- a/artfynd/A 45350-2024 artfynd.xlsx
+++ b/artfynd/A 45350-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120522233</v>
+        <v>120522599</v>
       </c>
       <c r="B2" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463348</v>
+        <v>463495</v>
       </c>
       <c r="R2" t="n">
-        <v>6720041</v>
+        <v>6720323</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120522226</v>
+        <v>120522965</v>
       </c>
       <c r="B3" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463359</v>
+        <v>463108</v>
       </c>
       <c r="R3" t="n">
-        <v>6720025</v>
+        <v>6720174</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120522965</v>
+        <v>120522185</v>
       </c>
       <c r="B4" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463108</v>
+        <v>463394</v>
       </c>
       <c r="R4" t="n">
-        <v>6720174</v>
+        <v>6719985</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120522767</v>
+        <v>120522233</v>
       </c>
       <c r="B5" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463536</v>
+        <v>463348</v>
       </c>
       <c r="R5" t="n">
-        <v>6720348</v>
+        <v>6720041</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,44 +1079,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120522747</v>
+        <v>120522767</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463506</v>
+        <v>463536</v>
       </c>
       <c r="R6" t="n">
-        <v>6720334</v>
+        <v>6720348</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1207,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120522728</v>
+        <v>120522226</v>
       </c>
       <c r="B7" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463492</v>
+        <v>463359</v>
       </c>
       <c r="R7" t="n">
-        <v>6720346</v>
+        <v>6720025</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1313,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120522599</v>
+        <v>120522728</v>
       </c>
       <c r="B8" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463495</v>
+        <v>463492</v>
       </c>
       <c r="R8" t="n">
-        <v>6720323</v>
+        <v>6720346</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1419,42 +1382,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120522185</v>
+        <v>120522747</v>
       </c>
       <c r="B9" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463394</v>
+        <v>463506</v>
       </c>
       <c r="R9" t="n">
-        <v>6719985</v>
+        <v>6720334</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 45350-2024 artfynd.xlsx
+++ b/artfynd/A 45350-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522226</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522728</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,8 +1522,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120522747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>